--- a/review/abilities/workbooks/22_Class_Intellect.xlsx
+++ b/review/abilities/workbooks/22_Class_Intellect.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -197,7 +197,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -234,19 +234,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1039,8 +1026,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1209,42 +1196,42 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>An accessible person, object or scene with evidence you can examine.</t>
+          <t>Self; one case, person, place or problem you have been investigating.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Spend one minute examining the evidence and state a question. Learn one supported fact relevant to it and a specific way to investigate further: a person to question, place to examine or test to perform, if one exists. If the evidence cannot answer your question, learn what kind of evidence is missing.</t>
+          <t>Spend one minute reviewing what you know. The DA reveals one missed detail grounded in established facts.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Spend one minute examining the evidence and state a question. Learn one supported fact relevant to it and a specific way to investigate further: a person to question, place to examine or test to perform, if one exists. If the evidence cannot answer your question, learn what kind of evidence is missing. No roll; obvious clues remain available to everyone. This does not reveal thoughts or invent events.</t>
+          <t>Spend one minute reviewing everything you have learned about one case, person, place or problem. You must have at least one relevant fact or observation. The DA reveals one detail you missed, grounded in the facts already established: a piece of evidence, a motivation, a tell, an angle or a connection.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>One-minute evidence analysis yielding a supported fact and a concrete lead; strong investigation pillar.</t>
+          <t>Case-wide insight: one minute of review and the DA reveals one missed detail grounded in established facts. Strong noncombat investigation pillar.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Overlaps with Test the Hypothesis. Differentiate by scale (single fact vs sequence) and make the one-minute cost explicit in play guidance.</t>
+          <t>Approved: Main Action, one minute, one case/person/place/problem, requires at least one relevant fact; the DA reveals one missed detail grounded in established facts.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1258,52 +1245,52 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-intellect-prepared-explanation</t>
+          <t>Angle of Attack</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One ally within 3 squares that can hear and understand your Aid.</t>
+          <t>One creature within reach of your melee weapon. You must be wielding a melee weapon.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Your Aid can reach that ally. When you give Aid, the ally may also move 1 square without provoking before making the aided roll. This movement uses no ally action or movement allowance. Aid’s Boon and expiry are unchanged.</t>
+          <t>Knowledge-based melee weapon attack for 3/5/7 physical damage.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Your Aid can reach that ally. When you give Aid, the ally may also move 1 square without provoking before making the aided roll. This movement uses no ally action or movement allowance. Aid’s Boon and expiry are unchanged.</t>
+          <t>Make a melee weapon attack against one creature within reach, using Knowledge instead of Brawn. On a Weak result, deal 3 physical damage. On a Standard result, deal 5 physical damage. On a Strong result, deal 7 physical damage.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Aid reaches 3 squares and the ally moves 1 before the aided roll; good action compression.</t>
+          <t>Angle of Attack: Knowledge-based melee weapon attack for 3/5/7 physical damage. Gives the Intellect a credible intelligent-fighter attack and direct combat agency.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the ally's movement can leave melee and whether it provokes (no). Add an example of a valid Aid task.</t>
+          <t>Approved: Main Action, Knowledge instead of Brawn, melee weapon required, 3/5/7 physical damage, repeatable with normal action economy.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1327,42 +1314,42 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One visible ordinary obstacle within 3 squares.</t>
+          <t>One visible creature or obstacle within 5 squares; you and each ally within 5 squares who can hear and understand you.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Learn whether Force can overcome it, its remaining progress target, and one practical point at which to apply force. You or one ally who can hear your explanation gains 2 Boons to the next Force action against that obstacle before the scene ends. No permission to force an impossible obstacle is granted.</t>
+          <t>Learn one defense or visible weakness on a creature, or whether Force can overcome an obstacle and its progress target. You and nearby allies gain 1 Boon to your next action against it.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Learn whether Force can overcome it, its remaining progress target, and one practical point at which to apply force. You or one ally who can hear your explanation gains 2 Boons to the next Force action against that obstacle before the scene ends. No permission to force an impossible obstacle is granted.</t>
+          <t>Choose one visible creature or obstacle within 5 squares. Learn one useful opening: for a creature, one of its defenses or one visible weakness; for an obstacle, whether Force can overcome it and its remaining progress target. You and each ally within 5 squares who can hear and understand you gain 1 Boon to your next action against the target before the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver to learn an obstacle's progress target and grant 2 Boons to the next Force action. Very strong with a Force-focused ally.</t>
+          <t>Tactical read on a creature or obstacle, granting the Intellect and nearby allies 1 Boon to their next action against it. Gives Intellect a proactive combat option and scales into Expose the Mechanism.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Consider 1 Boon if it proves dominant. Clarify whether the Boons stack with other analysis effects and whether they apply to the Intellect's own Force action.</t>
+          <t>Approved: Maneuver; visible creature or obstacle within 5; learn one defense or visible weakness, or obstacle Force/progress information; Intellect and hearing allies within 5 gain 1 Boon; one application per target per scene.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1385,15 +1372,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1535,7 +1519,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1545,32 +1529,32 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>The ally may move up to 3 squares without provoking. It gains 1 Boon to its next roll before the start of your next turn if that roll acts on a visible objective you name when using this card. The ally chooses whether and how to act; this grants no attack.</t>
+          <t>Ally moves 3 without provoking, then makes one Basic Melee or Basic Ranged attack as part of your Maneuver, leaving their action available.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>The ally may move up to 3 squares without provoking. It gains 1 Boon to its next roll before the start of your next turn if that roll acts on a visible objective you name when using this card. The ally chooses whether and how to act; this grants no attack.</t>
+          <t>The ally may move up to 3 squares without provoking. The ally may then make one Basic Melee or Basic Ranged attack against a target they can see. That attack is part of your Maneuver, so the ally’s action remains available.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Ally moves 3 and gains a Boon on a named objective; strong positioning support.</t>
+          <t>Allied action compression: move 3 and make one Basic Melee or Basic Ranged attack as part of the Intellect's Maneuver, leaving the ally's action available. Strong level 3 support.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon can apply to an attack roll or only a skill roll. 'Next roll acting on the objective' could include attacks; decide and state it.</t>
+          <t>Approved: Maneuver; willing ally within 4; move 3 without provoking; one Basic Melee or Basic Ranged attack; does not use the ally's action; once on the Intellect's turn.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1589,47 +1573,47 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One accessible ordinary mechanism, damaged or functioning.</t>
+          <t>One ally within 5 squares that can hear and understand you, after a Weak result on that ally’s attack or skill roll.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Examine it for one minute. Learn its purpose, its working parts and a specific safe way to disable or repair it, if one exists. You can perform a simple accessible adjustment with suitable tools during that minute; a job requiring materials, dismantling or crafting still needs its usual permission and work.</t>
+          <t>Diagnose the mistake; the ally may reroll the attack or skill roll with 1 Boon.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Examine it for one minute. Learn its purpose, its working parts and a specific safe way to disable or repair it, if one exists. You can perform a simple accessible adjustment with suitable tools during that minute; a job requiring materials, dismantling or crafting still needs its usual permission and work. For such a job, you or one ally gains 2 Boons to the next appropriate roll following your diagnosis. This does not reveal a magical mechanism or a recipe.</t>
+          <t>Diagnose the mistake and show the ally the correction. The ally may reroll the roll with 1 Boon. The reroll is part of your Reaction; the ally keeps their own Reaction.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>One-minute mechanism diagnosis with 2 Boons to a follow-up roll; strong utility and a clear noncombat identity.</t>
+          <t>Reaction support: when an ally within 5 has a Weak attack or skill result, the ally rerolls with 1 Boon. Strong once-per-round correction.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify the interaction with magical mechanisms (text excludes them) and whether the Boons can be split between allies.</t>
+          <t>Approved: Reaction, ally within 5 who can hear and understand, Weak attack or skill result, reroll with 1 Boon, once per round, uses the Intellect Reaction.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1648,47 +1632,47 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self or one willing ally within 3 squares, before defending against a visible physical attack.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>The recipient may use Reason for this defense instead of its normal attribute and gains 1 Boon to the roll. An ally must hear and understand your warning. Resolve the ordinary defense once. This does not apply to poison, internal injury or mental intrusion.</t>
+          <t>Use Knowledge instead of Brawn or Agility for defense against physical attacks.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>The recipient may use Reason for this defense instead of its normal attribute and gains 1 Boon to the roll. An ally must hear and understand your warning. Resolve the ordinary defense once. This does not apply to poison, internal injury or mental intrusion.</t>
+          <t>You may use Knowledge instead of Brawn or Agility for defense against physical attacks.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Reaction to let self or an ally use Reason for a physical defense and gain 1 Boon; strong defensive support.</t>
+          <t>Passive Knowledge defense against all physical attacks. Removes the Reaction conflict and gives the knowledge-based fighter a clear combat identity.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Very efficient; monitor. Clarify that the ally must hear you before the attack is declared and whether it applies to ranged attacks (text says visible physical attack).</t>
+          <t>Approved: Passive; use Knowledge instead of Brawn or Agility for defense against physical attacks.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1711,15 +1695,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1861,7 +1842,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1871,12 +1852,12 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Each recipient may move up to 3 squares without provoking, in an order you choose. Each gains 1 Boon to its next defense before the start of your next turn. Choose legal routes and separate free endpoints; this grants no attacks.</t>
+          <t>Up to four recipients move 3 squares without provoking and gain 1 Boon to their next defense.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Each recipient may move up to 3 squares without provoking, in an order you choose. Each gains 1 Boon to its next defense before the start of your next turn. Choose legal routes and separate free endpoints; this grants no attacks.</t>
+          <t>Each recipient may move up to 3 squares without provoking, in an order you choose. Each gains 1 Boon to its next defense before the start of your next turn. Choose legal routes and separate free endpoints.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -1886,17 +1867,17 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Very strong; monitor. Clarify whether allies can move in any order and whether the Boon applies if they move out of your sight.</t>
+          <t>Approved: positive wording only. Each recipient moves 3 without provoking in an order you choose and gains 1 Boon to its next defense.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Power spike</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1910,52 +1891,52 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-intellect-expose-the-mechanism</t>
+          <t>Shatter the Guard</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One visible creature or active device within 5 squares; up to two allies within 5 squares that can hear you.</t>
+          <t>One visible creature or active device within 5 squares; one ally within 5 squares who can hear and understand you.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Learn one actual resistance and one actual weakness of the target, if present, and one capability you have seen it use in this scene. The DA explains that capability’s visible trigger or limitation. Each chosen ally gains 1 Boon to its next roll against that target before the start of your next turn.</t>
+          <t>Knowledge attack for 5/7/9 physical damage; strip 1 resistance for the scene and give one ally a Boon against the target.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Learn one actual resistance and one actual weakness of the target, if present, and one capability you have seen it use in this scene. The DA explains that capability’s visible trigger or limitation. Each chosen ally gains 1 Boon to its next roll against that target before the start of your next turn. No weakness is created and no resistance is reduced.</t>
+          <t>Make a Knowledge-based attack against the target. On a Weak result, deal 5 physical damage. On a Standard result, deal 7 physical damage. On a Strong result, deal 9 physical damage. The target loses 1 resistance of your choice until the end of the scene, and the chosen ally gains 1 Boon to their next attack against it before the start of your next turn.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Maneuver to reveal one resistance and one weakness and give two allies a Boon; strong Master support.</t>
+          <t>Shatter the Guard: Main Action Knowledge attack for 5/7/9 physical damage, strip 1 resistance for the scene, and give one ally a Boon against the target. Clean Master attack and support.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Overlaps with Warden Know What You Hunt. Differentiate by immediacy (Intellect is combat-time, Warden is scene-long) and clarify whether 'resistance' includes immunities.</t>
+          <t>Approved: Main Action, Knowledge attack, 5/7/9 physical, target loses 1 resistance of choice until end of scene, one ally within 5 gains 1 Boon against it, one resistance reduction per target per scene.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1979,42 +1960,42 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>An accessible evidence set and one question about what happened.</t>
+          <t>Self and up to three allies who can hear and understand you.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Spend ten minutes examining the evidence. Obtain a supported sequence of events answering your question as far as the evidence allows. The DA states what remains uncertain, one contradiction in your explanation if the evidence contains one, and a concrete lead for checking it if one exists.</t>
+          <t>Spend one minute forming a plan. The DA confirms truth, uncertainty and one risk; each participant gains 2 Boons to a roll following the plan.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Spend ten minutes examining the evidence. Obtain a supported sequence of events answering your question as far as the evidence allows. The DA states what remains uncertain, one contradiction in your explanation if the evidence contains one, and a concrete lead for checking it if one exists. Share the account with your companions; they need no duplicate interpretation rolls. No secret facts are invented.</t>
+          <t>Spend one minute forming a plan from the evidence and observations available. State the plan. The DA confirms what is true, what remains uncertain, and one contradiction or risk. You and each chosen ally gain 2 Boons to your next roll that directly follows the plan.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Ten-minute evidence analysis yielding a sequence, uncertainty, contradiction and lead; strong Master investigation.</t>
+          <t>Master plan: one minute with up to three allies; the DA confirms truth, uncertainty and one risk; each participant gains 2 Boons to a roll that follows the plan. Strong pre-scene planning capstone.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Overlaps with Make the Connection. Ensure the Master version is clearly bigger and say whether it can be used during a scene with immediate stakes.</t>
+          <t>Approved: Main Action, one minute, self plus up to three allies, DA confirms truth/uncertainty/risk, 2 Boons each to a roll following the plan, once per scene.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -2037,15 +2018,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2192,27 +2170,27 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>An accessible person, object or scene with evidence you can examine.</t>
+          <t>Self; one case, person, place or problem you have been investigating.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Spend one minute examining the evidence and state a question. Learn one supported fact relevant to it and a specific way to investigate further: a person to question, place to examine or test to perform, if one exists. If the evidence cannot answer your question, learn what kind of evidence is missing.</t>
+          <t>Spend one minute reviewing what you know. The DA reveals one missed detail grounded in established facts.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>One-minute evidence analysis yielding a supported fact and a concrete lead; strong investigation pillar.</t>
+          <t>Case-wide insight: one minute of review and the DA reveals one missed detail grounded in established facts. Strong noncombat investigation pillar.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Overlaps with Test the Hypothesis. Differentiate by scale (single fact vs sequence) and make the one-minute cost explicit in play guidance.</t>
+          <t>Approved: Main Action, one minute, one case/person/place/problem, requires at least one relevant fact; the DA reveals one missed detail grounded in established facts.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2236,7 +2214,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Prepared Explanation</t>
+          <t>Angle of Attack</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2246,32 +2224,32 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>One ally within 3 squares that can hear and understand your Aid.</t>
+          <t>One creature within reach of your melee weapon. You must be wielding a melee weapon.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Your Aid can reach that ally. When you give Aid, the ally may also move 1 square without provoking before making the aided roll. This movement uses no ally action or movement allowance. Aid’s Boon and expiry are unchanged.</t>
+          <t>Knowledge-based melee weapon attack for 3/5/7 physical damage.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Aid reaches 3 squares and the ally moves 1 before the aided roll; good action compression.</t>
+          <t>Angle of Attack: Knowledge-based melee weapon attack for 3/5/7 physical damage. Gives the Intellect a credible intelligent-fighter attack and direct combat agency.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the ally's movement can leave melee and whether it provokes (no). Add an example of a valid Aid task.</t>
+          <t>Approved: Main Action, Knowledge instead of Brawn, melee weapon required, 3/5/7 physical damage, repeatable with normal action economy.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -2310,27 +2288,27 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>One visible ordinary obstacle within 3 squares.</t>
+          <t>One visible creature or obstacle within 5 squares; you and each ally within 5 squares who can hear and understand you.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Learn whether Force can overcome it, its remaining progress target, and one practical point at which to apply force. You or one ally who can hear your explanation gains 2 Boons to the next Force action against that obstacle before the scene ends. No permission to force an impossible obstacle is granted.</t>
+          <t>Learn one defense or visible weakness on a creature, or whether Force can overcome an obstacle and its progress target. You and nearby allies gain 1 Boon to your next action against it.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver to learn an obstacle's progress target and grant 2 Boons to the next Force action. Very strong with a Force-focused ally.</t>
+          <t>Tactical read on a creature or obstacle, granting the Intellect and nearby allies 1 Boon to their next action against it. Gives Intellect a proactive combat option and scales into Expose the Mechanism.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Consider 1 Boon if it proves dominant. Clarify whether the Boons stack with other analysis effects and whether they apply to the Intellect's own Force action.</t>
+          <t>Approved: Maneuver; visible creature or obstacle within 5; learn one defense or visible weakness, or obstacle Force/progress information; Intellect and hearing allies within 5 gain 1 Boon; one application per target per scene.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2369,7 +2347,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2379,17 +2357,17 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>The ally may move up to 3 squares without provoking. It gains 1 Boon to its next roll before the start of your next turn if that roll acts on a visible objective you name when using this card. The ally chooses whether and how to act; this grants no attack.</t>
+          <t>Ally moves 3 without provoking, then makes one Basic Melee or Basic Ranged attack as part of your Maneuver, leaving their action available.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Ally moves 3 and gains a Boon on a named objective; strong positioning support.</t>
+          <t>Allied action compression: move 3 and make one Basic Melee or Basic Ranged attack as part of the Intellect's Maneuver, leaving the ally's action available. Strong level 3 support.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon can apply to an attack roll or only a skill roll. 'Next roll acting on the objective' could include attacks; decide and state it.</t>
+          <t>Approved: Maneuver; willing ally within 4; move 3 without provoking; one Basic Melee or Basic Ranged attack; does not use the ally's action; once on the Intellect's turn.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -2423,32 +2401,32 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>One accessible ordinary mechanism, damaged or functioning.</t>
+          <t>One ally within 5 squares that can hear and understand you, after a Weak result on that ally’s attack or skill roll.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Examine it for one minute. Learn its purpose, its working parts and a specific safe way to disable or repair it, if one exists. You can perform a simple accessible adjustment with suitable tools during that minute; a job requiring materials, dismantling or crafting still needs its usual permission and work.</t>
+          <t>Diagnose the mistake; the ally may reroll the attack or skill roll with 1 Boon.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>One-minute mechanism diagnosis with 2 Boons to a follow-up roll; strong utility and a clear noncombat identity.</t>
+          <t>Reaction support: when an ally within 5 has a Weak attack or skill result, the ally rerolls with 1 Boon. Strong once-per-round correction.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Clarify the interaction with magical mechanisms (text excludes them) and whether the Boons can be split between allies.</t>
+          <t>Approved: Reaction, ally within 5 who can hear and understand, Weak attack or skill result, reroll with 1 Boon, once per round, uses the Intellect Reaction.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -2482,32 +2460,32 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Self or one willing ally within 3 squares, before defending against a visible physical attack.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>The recipient may use Reason for this defense instead of its normal attribute and gains 1 Boon to the roll. An ally must hear and understand your warning. Resolve the ordinary defense once. This does not apply to poison, internal injury or mental intrusion.</t>
+          <t>Use Knowledge instead of Brawn or Agility for defense against physical attacks.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Reaction to let self or an ally use Reason for a physical defense and gain 1 Boon; strong defensive support.</t>
+          <t>Passive Knowledge defense against all physical attacks. Removes the Reaction conflict and gives the knowledge-based fighter a clear combat identity.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Very efficient; monitor. Clarify that the ally must hear you before the attack is declared and whether it applies to ranged attacks (text says visible physical attack).</t>
+          <t>Approved: Passive; use Knowledge instead of Brawn or Agility for defense against physical attacks.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2546,7 +2524,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2556,7 +2534,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Each recipient may move up to 3 squares without provoking, in an order you choose. Each gains 1 Boon to its next defense before the start of your next turn. Choose legal routes and separate free endpoints; this grants no attacks.</t>
+          <t>Up to four recipients move 3 squares without provoking and gain 1 Boon to their next defense.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2566,7 +2544,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Very strong; monitor. Clarify whether allies can move in any order and whether the Boon applies if they move out of your sight.</t>
+          <t>Approved: positive wording only. Each recipient moves 3 without provoking in an order you choose and gains 1 Boon to its next defense.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -2590,7 +2568,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Expose the Mechanism</t>
+          <t>Shatter the Guard</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2600,32 +2578,32 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>One visible creature or active device within 5 squares; up to two allies within 5 squares that can hear you.</t>
+          <t>One visible creature or active device within 5 squares; one ally within 5 squares who can hear and understand you.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Learn one actual resistance and one actual weakness of the target, if present, and one capability you have seen it use in this scene. The DA explains that capability’s visible trigger or limitation. Each chosen ally gains 1 Boon to its next roll against that target before the start of your next turn.</t>
+          <t>Knowledge attack for 5/7/9 physical damage; strip 1 resistance for the scene and give one ally a Boon against the target.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Maneuver to reveal one resistance and one weakness and give two allies a Boon; strong Master support.</t>
+          <t>Shatter the Guard: Main Action Knowledge attack for 5/7/9 physical damage, strip 1 resistance for the scene, and give one ally a Boon against the target. Clean Master attack and support.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Overlaps with Warden Know What You Hunt. Differentiate by immediacy (Intellect is combat-time, Warden is scene-long) and clarify whether 'resistance' includes immunities.</t>
+          <t>Approved: Main Action, Knowledge attack, 5/7/9 physical, target loses 1 resistance of choice until end of scene, one ally within 5 gains 1 Boon against it, one resistance reduction per target per scene.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2664,27 +2642,27 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>An accessible evidence set and one question about what happened.</t>
+          <t>Self and up to three allies who can hear and understand you.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Spend ten minutes examining the evidence. Obtain a supported sequence of events answering your question as far as the evidence allows. The DA states what remains uncertain, one contradiction in your explanation if the evidence contains one, and a concrete lead for checking it if one exists.</t>
+          <t>Spend one minute forming a plan. The DA confirms truth, uncertainty and one risk; each participant gains 2 Boons to a roll following the plan.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Ten-minute evidence analysis yielding a sequence, uncertainty, contradiction and lead; strong Master investigation.</t>
+          <t>Master plan: one minute with up to three allies; the DA confirms truth, uncertainty and one risk; each participant gains 2 Boons to a roll that follows the plan. Strong pre-scene planning capstone.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Overlaps with Make the Connection. Ensure the Master version is clearly bigger and say whether it can be used during a scene with immediate stakes.</t>
+          <t>Approved: Main Action, one minute, self plus up to three allies, DA confirms truth/uncertainty/risk, 2 Boons each to a roll following the plan, once per scene.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -2717,15 +2695,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3289,15 +3264,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3321,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3336,12 +3308,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3422,30 +3393,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3469,7 +3435,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3489,7 +3454,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3509,7 +3473,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3529,7 +3492,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3549,7 +3511,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3569,7 +3530,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3589,7 +3549,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3609,7 +3568,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3629,7 +3587,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3649,7 +3606,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3669,7 +3625,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3689,23 +3644,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
